--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>85.04095739016996</v>
+        <v>13.81915557590262</v>
       </c>
       <c r="D2" t="n">
-        <v>35.17610454246707</v>
+        <v>5.716116988150899</v>
       </c>
       <c r="E2" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F2" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>106.6078387284078</v>
+        <v>17.32377379336626</v>
       </c>
       <c r="D3" t="n">
-        <v>68.95234643557487</v>
+        <v>11.20475629578092</v>
       </c>
       <c r="E3" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F3" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>61.8059210328861</v>
+        <v>10.04346216784399</v>
       </c>
       <c r="D4" t="n">
-        <v>12.80986907186019</v>
+        <v>2.081603724177282</v>
       </c>
       <c r="E4" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F4" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>72.44201507246639</v>
+        <v>11.77182744927579</v>
       </c>
       <c r="D5" t="n">
-        <v>34.44739538293866</v>
+        <v>5.597701749727532</v>
       </c>
       <c r="E5" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F5" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>56.40660859847938</v>
+        <v>9.1660738972529</v>
       </c>
       <c r="D6" t="n">
-        <v>8.909418789485711</v>
+        <v>1.447780553291428</v>
       </c>
       <c r="E6" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F6" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>51.39862507796996</v>
+        <v>8.352276575170119</v>
       </c>
       <c r="D7" t="n">
-        <v>2.995251828642807</v>
+        <v>0.4867284221544562</v>
       </c>
       <c r="E7" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F7" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>49.10411206182367</v>
+        <v>7.979418210046346</v>
       </c>
       <c r="D8" t="n">
-        <v>9.814529979811564</v>
+        <v>1.594861121719379</v>
       </c>
       <c r="E8" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F8" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>67.05955925013298</v>
+        <v>10.89717837814661</v>
       </c>
       <c r="D9" t="n">
-        <v>30.31134734349131</v>
+        <v>4.925593943317338</v>
       </c>
       <c r="E9" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F9" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>84.53339593280698</v>
+        <v>13.73667683908113</v>
       </c>
       <c r="D10" t="n">
-        <v>64.76151590280647</v>
+        <v>10.52374633420605</v>
       </c>
       <c r="E10" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F10" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>43.94831912285484</v>
+        <v>7.141601857463912</v>
       </c>
       <c r="D11" t="n">
-        <v>10.06464725623599</v>
+        <v>1.635505179138349</v>
       </c>
       <c r="E11" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F11" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>44.25025671498491</v>
+        <v>7.190666716185047</v>
       </c>
       <c r="D12" t="n">
-        <v>8.594520804327649</v>
+        <v>1.396609630703243</v>
       </c>
       <c r="E12" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F12" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>48.01994477831578</v>
+        <v>7.803241026476315</v>
       </c>
       <c r="D13" t="n">
-        <v>9.093648577135824</v>
+        <v>1.477717893784571</v>
       </c>
       <c r="E13" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F13" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>40.5511691049651</v>
+        <v>6.58956497955683</v>
       </c>
       <c r="D14" t="n">
-        <v>11.79271198148981</v>
+        <v>1.916315696992094</v>
       </c>
       <c r="E14" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F14" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>50.11753335187606</v>
+        <v>8.14409916967986</v>
       </c>
       <c r="D15" t="n">
-        <v>27.10624027805526</v>
+        <v>4.40476404518398</v>
       </c>
       <c r="E15" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F15" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>33.53948517266943</v>
+        <v>5.450166340558782</v>
       </c>
       <c r="D16" t="n">
-        <v>15.55762563295472</v>
+        <v>2.528114165355142</v>
       </c>
       <c r="E16" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F16" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>61.79593386131863</v>
+        <v>10.04183925246428</v>
       </c>
       <c r="D17" t="n">
-        <v>48.18338095426321</v>
+        <v>7.829799405067773</v>
       </c>
       <c r="E17" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F17" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>26.11102313927983</v>
+        <v>4.243041260132972</v>
       </c>
       <c r="D18" t="n">
-        <v>25.17163306404872</v>
+        <v>4.090390372907918</v>
       </c>
       <c r="E18" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F18" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>80.6412158707866</v>
+        <v>13.10419757900282</v>
       </c>
       <c r="D19" t="n">
-        <v>73.56177791408132</v>
+        <v>11.95378891103821</v>
       </c>
       <c r="E19" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F19" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>29.68193505080102</v>
+        <v>4.823314445755165</v>
       </c>
       <c r="D20" t="n">
-        <v>28.13045308380099</v>
+        <v>4.571198626117662</v>
       </c>
       <c r="E20" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F20" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>43.39006933927081</v>
+        <v>7.050886267631506</v>
       </c>
       <c r="D21" t="n">
-        <v>39.93011829792322</v>
+        <v>6.488644223412523</v>
       </c>
       <c r="E21" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F21" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>17.26702508526056</v>
+        <v>2.805891576354841</v>
       </c>
       <c r="D22" t="n">
-        <v>17.1050441335117</v>
+        <v>2.779569671695652</v>
       </c>
       <c r="E22" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F22" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>26.11793298456454</v>
+        <v>4.244164109991738</v>
       </c>
       <c r="D23" t="n">
-        <v>25.82631009026624</v>
+        <v>4.196775389668264</v>
       </c>
       <c r="E23" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F23" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>9.077966715743132</v>
+        <v>1.475169591308259</v>
       </c>
       <c r="D24" t="n">
-        <v>9.66925095499532</v>
+        <v>1.57125328018674</v>
       </c>
       <c r="E24" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F24" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>20.58727208249037</v>
+        <v>3.345431713404686</v>
       </c>
       <c r="D25" t="n">
-        <v>21.13257093391627</v>
+        <v>3.434042776761394</v>
       </c>
       <c r="E25" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F25" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>5.673471737348847</v>
+        <v>0.9219391573191876</v>
       </c>
       <c r="D26" t="n">
-        <v>4.527363050149723</v>
+        <v>0.73569649564933</v>
       </c>
       <c r="E26" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F26" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>40.8662387846014</v>
+        <v>6.640763802497728</v>
       </c>
       <c r="D27" t="n">
-        <v>40.63425433523646</v>
+        <v>6.603066329475924</v>
       </c>
       <c r="E27" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F27" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>48.70314188455956</v>
+        <v>7.914260556240929</v>
       </c>
       <c r="D28" t="n">
-        <v>28.04460732476032</v>
+        <v>4.557248690273552</v>
       </c>
       <c r="E28" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F28" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>21.93433479777284</v>
+        <v>3.564329404638087</v>
       </c>
       <c r="D29" t="n">
-        <v>12.13030310455822</v>
+        <v>1.971174254490712</v>
       </c>
       <c r="E29" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F29" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>49.17930396769189</v>
+        <v>7.991636894749933</v>
       </c>
       <c r="D30" t="n">
-        <v>36.06226660205765</v>
+        <v>5.860118322834368</v>
       </c>
       <c r="E30" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F30" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>40.23795418766981</v>
+        <v>6.538667555496344</v>
       </c>
       <c r="D31" t="n">
-        <v>9.300537618869138</v>
+        <v>1.511337363066235</v>
       </c>
       <c r="E31" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F31" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>45.84348588386408</v>
+        <v>7.449566456127912</v>
       </c>
       <c r="D32" t="n">
-        <v>10.30776406404415</v>
+        <v>1.675011660407175</v>
       </c>
       <c r="E32" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F32" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>46.31201434791475</v>
+        <v>7.525702331536148</v>
       </c>
       <c r="D33" t="n">
-        <v>15.23154621172782</v>
+        <v>2.475126259405771</v>
       </c>
       <c r="E33" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F33" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>74.19712900477198</v>
+        <v>12.05703346327545</v>
       </c>
       <c r="D34" t="n">
-        <v>49.20619879649311</v>
+        <v>7.996007304430131</v>
       </c>
       <c r="E34" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F34" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>25.98828054978544</v>
+        <v>4.223095589340134</v>
       </c>
       <c r="D35" t="n">
-        <v>14.80012260151808</v>
+        <v>2.405019922746688</v>
       </c>
       <c r="E35" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F35" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>35.94724528425228</v>
+        <v>5.841427358690995</v>
       </c>
       <c r="D36" t="n">
-        <v>7.524037630626711</v>
+        <v>1.22265611497684</v>
       </c>
       <c r="E36" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F36" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>25.02586352210416</v>
+        <v>4.066702822341926</v>
       </c>
       <c r="D37" t="n">
-        <v>15.39271999857792</v>
+        <v>2.501316999768912</v>
       </c>
       <c r="E37" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F37" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>27.80987852212653</v>
+        <v>4.519105259845562</v>
       </c>
       <c r="D38" t="n">
-        <v>11.34268604086997</v>
+        <v>1.84318648164137</v>
       </c>
       <c r="E38" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F38" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>36.82096958321806</v>
+        <v>5.983407557272935</v>
       </c>
       <c r="D39" t="n">
-        <v>1.715113505388596</v>
+        <v>0.2787059446256468</v>
       </c>
       <c r="E39" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F39" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>18.49602501229026</v>
+        <v>3.005604064497167</v>
       </c>
       <c r="D40" t="n">
-        <v>19.55162133562746</v>
+        <v>3.177138467039462</v>
       </c>
       <c r="E40" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F40" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>38.5654634865641</v>
+        <v>6.266887816566666</v>
       </c>
       <c r="D41" t="n">
-        <v>8.417358785307728</v>
+        <v>1.367820802612506</v>
       </c>
       <c r="E41" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F41" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>14.3912693963058</v>
+        <v>2.338581276899692</v>
       </c>
       <c r="D42" t="n">
-        <v>13.38420171706764</v>
+        <v>2.174932779023491</v>
       </c>
       <c r="E42" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F42" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>49.99743203811979</v>
+        <v>8.124582706194467</v>
       </c>
       <c r="D43" t="n">
-        <v>29.97081914129142</v>
+        <v>4.870258110459855</v>
       </c>
       <c r="E43" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F43" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>10.02651013128743</v>
+        <v>1.629307896334208</v>
       </c>
       <c r="D44" t="n">
-        <v>9.790899862771377</v>
+        <v>1.591021227700349</v>
       </c>
       <c r="E44" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F44" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>86.66363034926034</v>
+        <v>14.08283993175481</v>
       </c>
       <c r="D45" t="n">
-        <v>66.74537020980887</v>
+        <v>10.84612265909394</v>
       </c>
       <c r="E45" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F45" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>7.988592909016631</v>
+        <v>1.298146347715203</v>
       </c>
       <c r="D46" t="n">
-        <v>9.233772581117458</v>
+        <v>1.500488044431587</v>
       </c>
       <c r="E46" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F46" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>81.35149354278471</v>
+        <v>13.21961770070252</v>
       </c>
       <c r="D47" t="n">
-        <v>63.95006732686926</v>
+        <v>10.39188594061626</v>
       </c>
       <c r="E47" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F47" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>70.37722524373453</v>
+        <v>11.43629910210686</v>
       </c>
       <c r="D48" t="n">
-        <v>53.77402296995101</v>
+        <v>8.738278732617038</v>
       </c>
       <c r="E48" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F48" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>17.07946402553507</v>
+        <v>2.77541290414945</v>
       </c>
       <c r="D49" t="n">
-        <v>15.6985267603796</v>
+        <v>2.551010598561684</v>
       </c>
       <c r="E49" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F49" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>30.79593282279496</v>
+        <v>5.00433908370418</v>
       </c>
       <c r="D50" t="n">
-        <v>16.49320095678018</v>
+        <v>2.680145155476779</v>
       </c>
       <c r="E50" t="n">
-        <v>23.54633640525145</v>
+        <v>3.82627966585336</v>
       </c>
       <c r="F50" t="n">
-        <v>19.07349639516766</v>
+        <v>3.099443164214744</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
